--- a/src/results/summary_results.xlsx
+++ b/src/results/summary_results.xlsx
@@ -488,25 +488,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="D2" t="n">
-        <v>271.89</v>
+        <v>266.68</v>
       </c>
       <c r="E2" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="F2" t="n">
-        <v>815677.0600000001</v>
+        <v>800044.22</v>
       </c>
       <c r="G2" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="H2" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="I2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J2" t="n">
         <v>175</v>
@@ -527,25 +527,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="D3" t="n">
-        <v>271.89</v>
+        <v>266.68</v>
       </c>
       <c r="E3" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="F3" t="n">
-        <v>815677.0600000001</v>
+        <v>800044.22</v>
       </c>
       <c r="G3" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="H3" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="I3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J3" t="n">
         <v>175</v>
@@ -566,25 +566,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="D4" t="n">
-        <v>271.89</v>
+        <v>266.68</v>
       </c>
       <c r="E4" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="F4" t="n">
-        <v>815677.0600000001</v>
+        <v>800044.22</v>
       </c>
       <c r="G4" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="H4" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="I4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J4" t="n">
         <v>175</v>
@@ -605,25 +605,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="D5" t="n">
-        <v>271.89</v>
+        <v>266.68</v>
       </c>
       <c r="E5" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="F5" t="n">
-        <v>815677.0600000001</v>
+        <v>800044.22</v>
       </c>
       <c r="G5" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="H5" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="I5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J5" t="n">
         <v>175</v>
@@ -644,25 +644,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.77</v>
+        <v>7.62</v>
       </c>
       <c r="D6" t="n">
-        <v>271.89</v>
+        <v>266.68</v>
       </c>
       <c r="E6" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="F6" t="n">
-        <v>815677.0600000001</v>
+        <v>800044.22</v>
       </c>
       <c r="G6" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="H6" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="I6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J6" t="n">
         <v>175</v>
@@ -683,25 +683,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.77</v>
+        <v>7.62</v>
       </c>
       <c r="D7" t="n">
-        <v>271.89</v>
+        <v>266.68</v>
       </c>
       <c r="E7" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="F7" t="n">
-        <v>815677.0600000001</v>
+        <v>800044.22</v>
       </c>
       <c r="G7" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="H7" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="I7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J7" t="n">
         <v>175</v>
@@ -722,25 +722,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.77</v>
+        <v>7.62</v>
       </c>
       <c r="D8" t="n">
-        <v>271.89</v>
+        <v>266.68</v>
       </c>
       <c r="E8" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="F8" t="n">
-        <v>815677.0600000001</v>
+        <v>800044.22</v>
       </c>
       <c r="G8" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="H8" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="I8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J8" t="n">
         <v>175</v>
@@ -761,25 +761,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.77</v>
+        <v>7.62</v>
       </c>
       <c r="D9" t="n">
-        <v>271.89</v>
+        <v>266.68</v>
       </c>
       <c r="E9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="F9" t="n">
-        <v>815677.0600000001</v>
+        <v>800044.22</v>
       </c>
       <c r="G9" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="H9" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="I9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J9" t="n">
         <v>175</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="E2" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="E3" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="F3" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="E4" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="F4" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="E5" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.77</v>
+        <v>7.62</v>
       </c>
       <c r="E6" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="F6" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7.77</v>
+        <v>7.62</v>
       </c>
       <c r="E7" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7.77</v>
+        <v>7.62</v>
       </c>
       <c r="E8" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.77</v>
+        <v>7.62</v>
       </c>
       <c r="E9" t="n">
-        <v>32.63</v>
+        <v>32</v>
       </c>
       <c r="F9" t="n">
-        <v>4661.01</v>
+        <v>4571.68</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>

--- a/src/results/summary_results.xlsx
+++ b/src/results/summary_results.xlsx
@@ -488,28 +488,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="D2" t="n">
-        <v>266.68</v>
+        <v>331.67</v>
       </c>
       <c r="E2" t="n">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
       <c r="F2" t="n">
-        <v>800044.22</v>
+        <v>995011.3100000001</v>
       </c>
       <c r="G2" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="H2" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="J2" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="D3" t="n">
-        <v>266.68</v>
+        <v>331.67</v>
       </c>
       <c r="E3" t="n">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
       <c r="F3" t="n">
-        <v>800044.22</v>
+        <v>995011.3100000001</v>
       </c>
       <c r="G3" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="H3" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="I3" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="J3" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -566,28 +566,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="D4" t="n">
-        <v>266.68</v>
+        <v>331.67</v>
       </c>
       <c r="E4" t="n">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
       <c r="F4" t="n">
-        <v>800044.22</v>
+        <v>995011.3100000001</v>
       </c>
       <c r="G4" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="H4" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="I4" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="J4" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -605,28 +605,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="D5" t="n">
-        <v>266.68</v>
+        <v>331.67</v>
       </c>
       <c r="E5" t="n">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
       <c r="F5" t="n">
-        <v>800044.22</v>
+        <v>995011.3100000001</v>
       </c>
       <c r="G5" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="H5" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="J5" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -644,28 +644,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.62</v>
+        <v>5.66</v>
       </c>
       <c r="D6" t="n">
-        <v>266.68</v>
+        <v>331.67</v>
       </c>
       <c r="E6" t="n">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
       <c r="F6" t="n">
-        <v>800044.22</v>
+        <v>995011.3100000001</v>
       </c>
       <c r="G6" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="H6" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="J6" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -683,28 +683,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.62</v>
+        <v>5.66</v>
       </c>
       <c r="D7" t="n">
-        <v>266.68</v>
+        <v>331.67</v>
       </c>
       <c r="E7" t="n">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
       <c r="F7" t="n">
-        <v>800044.22</v>
+        <v>995011.3100000001</v>
       </c>
       <c r="G7" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="H7" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="J7" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -722,28 +722,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.62</v>
+        <v>5.66</v>
       </c>
       <c r="D8" t="n">
-        <v>266.68</v>
+        <v>331.67</v>
       </c>
       <c r="E8" t="n">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
       <c r="F8" t="n">
-        <v>800044.22</v>
+        <v>995011.3100000001</v>
       </c>
       <c r="G8" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="H8" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="J8" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -761,28 +761,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.62</v>
+        <v>5.66</v>
       </c>
       <c r="D9" t="n">
-        <v>266.68</v>
+        <v>331.67</v>
       </c>
       <c r="E9" t="n">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
       <c r="F9" t="n">
-        <v>800044.22</v>
+        <v>995011.3100000001</v>
       </c>
       <c r="G9" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="H9" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="J9" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="F2" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="F3" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="F4" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="F5" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.62</v>
+        <v>5.66</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="F6" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7.62</v>
+        <v>5.66</v>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="F7" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7.62</v>
+        <v>5.66</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="F8" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.62</v>
+        <v>5.66</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="F9" t="n">
-        <v>4571.68</v>
+        <v>3395.94</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1244,25 +1244,25 @@
         <v>4.99</v>
       </c>
       <c r="D2" t="n">
-        <v>728.9400000000001</v>
+        <v>736.48</v>
       </c>
       <c r="E2" t="n">
         <v>2.5</v>
       </c>
       <c r="F2" t="n">
-        <v>2186837.99</v>
+        <v>2209459.49</v>
       </c>
       <c r="G2" t="n">
-        <v>7489.17</v>
+        <v>7489.69</v>
       </c>
       <c r="H2" t="n">
-        <v>87.48</v>
+        <v>88.38</v>
       </c>
       <c r="I2" t="n">
         <v>0.3</v>
       </c>
       <c r="J2" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1283,25 +1283,25 @@
         <v>4.99</v>
       </c>
       <c r="D3" t="n">
-        <v>728.9400000000001</v>
+        <v>736.48</v>
       </c>
       <c r="E3" t="n">
         <v>2.5</v>
       </c>
       <c r="F3" t="n">
-        <v>2186837.99</v>
+        <v>2209459.49</v>
       </c>
       <c r="G3" t="n">
-        <v>7489.17</v>
+        <v>7489.69</v>
       </c>
       <c r="H3" t="n">
-        <v>87.48</v>
+        <v>88.38</v>
       </c>
       <c r="I3" t="n">
         <v>0.3</v>
       </c>
       <c r="J3" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -1322,25 +1322,25 @@
         <v>4.99</v>
       </c>
       <c r="D4" t="n">
-        <v>728.9400000000001</v>
+        <v>736.48</v>
       </c>
       <c r="E4" t="n">
         <v>2.5</v>
       </c>
       <c r="F4" t="n">
-        <v>2186837.99</v>
+        <v>2209459.49</v>
       </c>
       <c r="G4" t="n">
-        <v>7489.17</v>
+        <v>7489.69</v>
       </c>
       <c r="H4" t="n">
-        <v>87.48</v>
+        <v>88.38</v>
       </c>
       <c r="I4" t="n">
         <v>0.3</v>
       </c>
       <c r="J4" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1361,25 +1361,25 @@
         <v>4.99</v>
       </c>
       <c r="D5" t="n">
-        <v>728.9400000000001</v>
+        <v>736.48</v>
       </c>
       <c r="E5" t="n">
         <v>2.5</v>
       </c>
       <c r="F5" t="n">
-        <v>2186837.99</v>
+        <v>2209459.49</v>
       </c>
       <c r="G5" t="n">
-        <v>7489.17</v>
+        <v>7489.69</v>
       </c>
       <c r="H5" t="n">
-        <v>87.48</v>
+        <v>88.38</v>
       </c>
       <c r="I5" t="n">
         <v>0.3</v>
       </c>
       <c r="J5" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1400,28 +1400,28 @@
         <v>11.3</v>
       </c>
       <c r="D6" t="n">
-        <v>737.29</v>
+        <v>744.97</v>
       </c>
       <c r="E6" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="F6" t="n">
-        <v>3353358.89</v>
+        <v>3394948.2</v>
       </c>
       <c r="G6" t="n">
-        <v>11484.11</v>
+        <v>11508.3</v>
       </c>
       <c r="H6" t="n">
-        <v>64.67</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>0.22</v>
       </c>
       <c r="J6" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K6" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7">
@@ -1439,28 +1439,28 @@
         <v>11.3</v>
       </c>
       <c r="D7" t="n">
-        <v>737.29</v>
+        <v>744.97</v>
       </c>
       <c r="E7" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="F7" t="n">
-        <v>3353358.89</v>
+        <v>3394948.2</v>
       </c>
       <c r="G7" t="n">
-        <v>11484.11</v>
+        <v>11508.3</v>
       </c>
       <c r="H7" t="n">
-        <v>64.67</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>0.22</v>
       </c>
       <c r="J7" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K7" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
@@ -1478,25 +1478,25 @@
         <v>12.48</v>
       </c>
       <c r="D8" t="n">
-        <v>728.9400000000001</v>
+        <v>736.48</v>
       </c>
       <c r="E8" t="n">
         <v>2.5</v>
       </c>
       <c r="F8" t="n">
-        <v>2186837.99</v>
+        <v>2209459.49</v>
       </c>
       <c r="G8" t="n">
-        <v>7489.17</v>
+        <v>7489.69</v>
       </c>
       <c r="H8" t="n">
-        <v>87.48</v>
+        <v>88.38</v>
       </c>
       <c r="I8" t="n">
         <v>0.3</v>
       </c>
       <c r="J8" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1517,25 +1517,25 @@
         <v>12.48</v>
       </c>
       <c r="D9" t="n">
-        <v>728.9400000000001</v>
+        <v>736.48</v>
       </c>
       <c r="E9" t="n">
         <v>2.5</v>
       </c>
       <c r="F9" t="n">
-        <v>2186837.99</v>
+        <v>2209459.49</v>
       </c>
       <c r="G9" t="n">
-        <v>7489.17</v>
+        <v>7489.69</v>
       </c>
       <c r="H9" t="n">
-        <v>87.48</v>
+        <v>88.38</v>
       </c>
       <c r="I9" t="n">
         <v>0.3</v>
       </c>
       <c r="J9" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1627,10 +1627,10 @@
         <v>4.99</v>
       </c>
       <c r="E2" t="n">
-        <v>87.48</v>
+        <v>88.38</v>
       </c>
       <c r="F2" t="n">
-        <v>7489.17</v>
+        <v>7489.69</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1665,10 +1665,10 @@
         <v>4.99</v>
       </c>
       <c r="E3" t="n">
-        <v>87.48</v>
+        <v>88.38</v>
       </c>
       <c r="F3" t="n">
-        <v>7489.17</v>
+        <v>7489.69</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1703,10 +1703,10 @@
         <v>4.99</v>
       </c>
       <c r="E4" t="n">
-        <v>87.48</v>
+        <v>88.38</v>
       </c>
       <c r="F4" t="n">
-        <v>7489.17</v>
+        <v>7489.69</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1741,10 +1741,10 @@
         <v>4.99</v>
       </c>
       <c r="E5" t="n">
-        <v>87.48</v>
+        <v>88.38</v>
       </c>
       <c r="F5" t="n">
-        <v>7489.17</v>
+        <v>7489.69</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1779,22 +1779,22 @@
         <v>11.3</v>
       </c>
       <c r="E6" t="n">
-        <v>64.67</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>11484.11</v>
+        <v>11508.3</v>
       </c>
       <c r="G6" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H6" t="n">
         <v>9.5</v>
       </c>
       <c r="I6" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="J6" t="n">
-        <v>-53.3</v>
+        <v>-53.7</v>
       </c>
     </row>
     <row r="7">
@@ -1817,22 +1817,22 @@
         <v>11.3</v>
       </c>
       <c r="E7" t="n">
-        <v>64.67</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>11484.11</v>
+        <v>11508.3</v>
       </c>
       <c r="G7" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H7" t="n">
         <v>9.5</v>
       </c>
       <c r="I7" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="J7" t="n">
-        <v>-53.3</v>
+        <v>-53.7</v>
       </c>
     </row>
     <row r="8">
@@ -1855,10 +1855,10 @@
         <v>12.48</v>
       </c>
       <c r="E8" t="n">
-        <v>87.48</v>
+        <v>88.38</v>
       </c>
       <c r="F8" t="n">
-        <v>7489.17</v>
+        <v>7489.69</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1893,10 +1893,10 @@
         <v>12.48</v>
       </c>
       <c r="E9" t="n">
-        <v>87.48</v>
+        <v>88.38</v>
       </c>
       <c r="F9" t="n">
-        <v>7489.17</v>
+        <v>7489.69</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
